--- a/進捗管理表/進捗管理表_奥川.xlsx
+++ b/進捗管理表/進捗管理表_奥川.xlsx
@@ -172,13 +172,13 @@
     <t xml:space="preserve">No.3→No.5 の処理</t>
   </si>
   <si>
-    <t xml:space="preserve">未着手</t>
-  </si>
-  <si>
     <t xml:space="preserve">登録のエラー画面</t>
   </si>
   <si>
     <t xml:space="preserve">タスク編集画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未着手</t>
   </si>
   <si>
     <t xml:space="preserve">タスク編集完了画面</t>
@@ -2659,8 +2659,8 @@
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
       <c r="L33" s="46"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
       <c r="O33" s="45"/>
       <c r="P33" s="45"/>
       <c r="Q33" s="45"/>
@@ -2753,8 +2753,8 @@
       <c r="J35" s="57"/>
       <c r="K35" s="57"/>
       <c r="L35" s="58"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="57"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
       <c r="O35" s="57"/>
       <c r="P35" s="57"/>
       <c r="Q35" s="57"/>
@@ -2847,8 +2847,8 @@
       <c r="J37" s="63"/>
       <c r="K37" s="63"/>
       <c r="L37" s="64"/>
-      <c r="M37" s="63"/>
-      <c r="N37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64"/>
       <c r="O37" s="63"/>
       <c r="P37" s="63"/>
       <c r="Q37" s="63"/>
@@ -2888,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F38" s="49" t="s">
         <v>18</v>
@@ -2942,7 +2942,7 @@
       <c r="K39" s="57"/>
       <c r="L39" s="57"/>
       <c r="M39" s="57"/>
-      <c r="N39" s="57"/>
+      <c r="N39" s="58"/>
       <c r="O39" s="57"/>
       <c r="P39" s="57"/>
       <c r="Q39" s="57"/>
@@ -2973,7 +2973,7 @@
         <v>5</v>
       </c>
       <c r="B40" s="70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" s="35" t="s">
         <v>22</v>
@@ -3035,8 +3035,8 @@
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
       <c r="L41" s="46"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
       <c r="O41" s="45"/>
       <c r="P41" s="45"/>
       <c r="Q41" s="45"/>
@@ -3153,7 +3153,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="35" t="s">
         <v>22</v>
@@ -3162,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F44" s="36" t="s">
         <v>18</v>
@@ -3256,7 +3256,7 @@
         <v>16</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F46" s="36" t="s">
         <v>18</v>
@@ -3350,7 +3350,7 @@
         <v>16</v>
       </c>
       <c r="E48" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F48" s="36" t="s">
         <v>18</v>
@@ -3444,7 +3444,7 @@
         <v>16</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F50" s="36" t="s">
         <v>18</v>
@@ -3538,7 +3538,7 @@
         <v>16</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F52" s="36" t="s">
         <v>18</v>
@@ -3674,7 +3674,7 @@
         <v>16</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F55" s="36" t="s">
         <v>18</v>
@@ -3768,7 +3768,7 @@
         <v>16</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F57" s="49" t="s">
         <v>18</v>
@@ -3862,7 +3862,7 @@
         <v>16</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F59" s="36" t="s">
         <v>18</v>
@@ -3956,7 +3956,7 @@
         <v>16</v>
       </c>
       <c r="E61" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F61" s="49" t="s">
         <v>18</v>
@@ -4264,7 +4264,7 @@
         <v>16</v>
       </c>
       <c r="E68" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F68" s="36" t="s">
         <v>18</v>

--- a/進捗管理表/進捗管理表_奥川.xlsx
+++ b/進捗管理表/進捗管理表_奥川.xlsx
@@ -3219,7 +3219,7 @@
       <c r="N45" s="45"/>
       <c r="O45" s="45"/>
       <c r="P45" s="45"/>
-      <c r="Q45" s="45"/>
+      <c r="Q45" s="46"/>
       <c r="R45" s="47"/>
       <c r="S45" s="44"/>
       <c r="T45" s="45"/>
@@ -3313,7 +3313,7 @@
       <c r="N47" s="45"/>
       <c r="O47" s="45"/>
       <c r="P47" s="45"/>
-      <c r="Q47" s="45"/>
+      <c r="Q47" s="46"/>
       <c r="R47" s="47"/>
       <c r="S47" s="44"/>
       <c r="T47" s="45"/>
@@ -3407,7 +3407,7 @@
       <c r="N49" s="45"/>
       <c r="O49" s="45"/>
       <c r="P49" s="45"/>
-      <c r="Q49" s="45"/>
+      <c r="Q49" s="46"/>
       <c r="R49" s="47"/>
       <c r="S49" s="44"/>
       <c r="T49" s="45"/>
@@ -3501,7 +3501,7 @@
       <c r="N51" s="45"/>
       <c r="O51" s="45"/>
       <c r="P51" s="45"/>
-      <c r="Q51" s="45"/>
+      <c r="Q51" s="46"/>
       <c r="R51" s="47"/>
       <c r="S51" s="44"/>
       <c r="T51" s="45"/>
@@ -3595,7 +3595,7 @@
       <c r="N53" s="45"/>
       <c r="O53" s="45"/>
       <c r="P53" s="45"/>
-      <c r="Q53" s="45"/>
+      <c r="Q53" s="46"/>
       <c r="R53" s="47"/>
       <c r="S53" s="44"/>
       <c r="T53" s="45"/>
